--- a/talklists/talklist.xlsx
+++ b/talklists/talklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/appforms/cv/talklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D42F450-1670-AC48-8DAA-A8F08F006126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6449455-F4D6-8C4D-91DA-6FC25330E81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2374,9 +2374,7 @@
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
-      <c r="R3" s="12">
-        <v>1</v>
-      </c>
+      <c r="R3" s="12"/>
     </row>
     <row r="4" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
@@ -2636,9 +2634,7 @@
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
-      <c r="R10" s="13">
-        <v>1</v>
-      </c>
+      <c r="R10" s="13"/>
     </row>
     <row r="11" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
@@ -2844,9 +2840,7 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
-      <c r="R15" s="12">
-        <v>1</v>
-      </c>
+      <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
@@ -2924,9 +2918,7 @@
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
-      <c r="R17" s="12">
-        <v>1</v>
-      </c>
+      <c r="R17" s="12"/>
     </row>
     <row r="18" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
@@ -3838,9 +3830,7 @@
       <c r="O40" s="23"/>
       <c r="P40" s="21"/>
       <c r="Q40" s="21"/>
-      <c r="R40" s="24">
-        <v>1</v>
-      </c>
+      <c r="R40" s="24"/>
     </row>
     <row r="41" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45" t="s">
@@ -3876,9 +3866,7 @@
       <c r="O41" s="23"/>
       <c r="P41" s="21"/>
       <c r="Q41" s="21"/>
-      <c r="R41" s="24">
-        <v>1</v>
-      </c>
+      <c r="R41" s="24"/>
     </row>
     <row r="42" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="44" t="s">
@@ -4040,6 +4028,9 @@
       <c r="K46" s="47">
         <v>1</v>
       </c>
+      <c r="R46" s="47">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="41" t="s">
@@ -4077,6 +4068,9 @@
       </c>
       <c r="Q47" s="49" t="s">
         <v>203</v>
+      </c>
+      <c r="R47" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/talklists/talklist.xlsx
+++ b/talklists/talklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/appforms/cv/talklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6449455-F4D6-8C4D-91DA-6FC25330E81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B895A20F-F73E-644E-B20C-740F6961BFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="209">
   <si>
     <t>title</t>
   </si>
@@ -844,12 +844,24 @@
     <t>Data Compression with Noise Suppression 
 for Inference under Noisy Covariance</t>
   </si>
+  <si>
+    <t>Observational Search for Primordial Black Holes Using Subaru/HSC Microlensing</t>
+  </si>
+  <si>
+    <t>Elucidating the Universe's Creation with Neutrinos based on International Science Collaborations</t>
+  </si>
+  <si>
+    <t>Ibe Masahiro</t>
+  </si>
+  <si>
+    <t>https://www-kam2.icrr.u-tokyo.ac.jp/event/19/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
@@ -884,6 +896,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1038,7 +1056,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1089,9 +1107,20 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2223,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="80.6640625" style="1" customWidth="1"/>
@@ -3800,37 +3829,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="45" t="s">
+    <row r="40" spans="1:18" s="40" customFormat="1" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21">
+      <c r="B40" s="51"/>
+      <c r="C40" s="51">
         <v>2024</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="51">
         <v>10</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="52" t="s">
         <v>177</v>
       </c>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21">
-        <v>1</v>
-      </c>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="41"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="21"/>
-      <c r="R40" s="24"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51">
+        <v>1</v>
+      </c>
+      <c r="L40" s="51"/>
+      <c r="M40" s="51"/>
+      <c r="N40" s="53"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="51"/>
+      <c r="R40" s="55"/>
     </row>
     <row r="41" spans="1:18" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45" t="s">
@@ -3942,38 +3971,38 @@
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="46" t="s">
+    <row r="44" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="57">
         <v>2025</v>
       </c>
-      <c r="D44" s="47">
+      <c r="D44" s="57">
         <v>9</v>
       </c>
-      <c r="E44" s="41" t="s">
+      <c r="E44" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="41" t="s">
+      <c r="F44" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="H44" s="47">
-        <v>1</v>
-      </c>
-      <c r="K44" s="47">
-        <v>1</v>
-      </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-      <c r="N44" s="41" t="s">
+      <c r="H44" s="57">
+        <v>1</v>
+      </c>
+      <c r="K44" s="57">
+        <v>1</v>
+      </c>
+      <c r="M44" s="40">
+        <v>1</v>
+      </c>
+      <c r="N44" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="O44" s="48" t="s">
+      <c r="O44" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="R44" s="47">
+      <c r="R44" s="57">
         <v>1</v>
       </c>
     </row>
@@ -4006,29 +4035,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="50" t="s">
+    <row r="46" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="57">
         <v>2025</v>
       </c>
-      <c r="D46" s="47">
+      <c r="D46" s="57">
         <v>11</v>
       </c>
-      <c r="E46" s="41" t="s">
+      <c r="E46" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="41" t="s">
+      <c r="F46" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="H46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="47">
-        <v>1</v>
-      </c>
-      <c r="R46" s="47">
+      <c r="H46" s="40">
+        <v>1</v>
+      </c>
+      <c r="K46" s="57">
+        <v>1</v>
+      </c>
+      <c r="R46" s="57">
         <v>1</v>
       </c>
     </row>
@@ -4073,6 +4102,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="48" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" s="57">
+        <v>2026</v>
+      </c>
+      <c r="D48" s="57">
+        <v>3</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="H48" s="40">
+        <v>1</v>
+      </c>
+      <c r="K48" s="57">
+        <v>1</v>
+      </c>
+      <c r="N48" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="O48" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="R48" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4107,6 +4170,7 @@
     <hyperlink ref="O43" r:id="rId30" xr:uid="{4F177060-0E22-8C42-B5E5-3DF784BED5A7}"/>
     <hyperlink ref="O44" r:id="rId31" xr:uid="{AF4601F7-8014-4F4E-9E9E-4A811C710B51}"/>
     <hyperlink ref="O47" r:id="rId32" location="20251205" xr:uid="{A78B1068-3E64-CE41-A412-3DC6F80D6967}"/>
+    <hyperlink ref="O48" r:id="rId33" xr:uid="{14BD41FF-A6AC-E24B-BEE2-CD42174C8935}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/talklists/talklist.xlsx
+++ b/talklists/talklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/appforms/cv/talklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B895A20F-F73E-644E-B20C-740F6961BFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6B43C7-B39E-1A40-84EB-09609667B43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="216">
   <si>
     <t>title</t>
   </si>
@@ -855,6 +855,27 @@
   </si>
   <si>
     <t>https://www-kam2.icrr.u-tokyo.ac.jp/event/19/</t>
+  </si>
+  <si>
+    <t>Cosmology from two- and three-point cosmic shear statistics</t>
+  </si>
+  <si>
+    <t>ASIAA</t>
+  </si>
+  <si>
+    <t>Cosmology group meeting</t>
+  </si>
+  <si>
+    <t>Searching for Primordial Black Holes with Microlensing Data from Subaru HSC</t>
+  </si>
+  <si>
+    <t>ASIAA colloquium</t>
+  </si>
+  <si>
+    <t>Tomomi Sunayama</t>
+  </si>
+  <si>
+    <t>https://www.asiaa.sinica.edu.tw/activity/colloquium.php</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1121,6 +1142,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4134,8 +4156,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="C49" s="47">
+        <v>2026</v>
+      </c>
+      <c r="D49" s="47">
+        <v>4</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="F49" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="47">
+        <v>1</v>
+      </c>
+      <c r="N49" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="O49" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="R49" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="C50" s="40">
+        <v>2026</v>
+      </c>
+      <c r="D50" s="40">
+        <v>4</v>
+      </c>
+      <c r="E50" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="F50" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="I50" s="40">
+        <v>1</v>
+      </c>
+      <c r="K50" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4171,6 +4247,7 @@
     <hyperlink ref="O44" r:id="rId31" xr:uid="{AF4601F7-8014-4F4E-9E9E-4A811C710B51}"/>
     <hyperlink ref="O47" r:id="rId32" location="20251205" xr:uid="{A78B1068-3E64-CE41-A412-3DC6F80D6967}"/>
     <hyperlink ref="O48" r:id="rId33" xr:uid="{14BD41FF-A6AC-E24B-BEE2-CD42174C8935}"/>
+    <hyperlink ref="O49" r:id="rId34" xr:uid="{7FA0972F-0B7F-834A-A6FD-87E313E18CDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/talklists/talklist.xlsx
+++ b/talklists/talklist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/appforms/cv/talklists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/writing/cv/talklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6B43C7-B39E-1A40-84EB-09609667B43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505ED053-D816-9142-853D-3EEEDDA05D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="220">
   <si>
     <t>title</t>
   </si>
@@ -876,6 +876,18 @@
   </si>
   <si>
     <t>https://www.asiaa.sinica.edu.tw/activity/colloquium.php</t>
+  </si>
+  <si>
+    <t>https://cosmophysics.gitlab.io/jointseminar.gitlab.io/sugiyama20260615.html</t>
+  </si>
+  <si>
+    <t>Probing Primordial Black Hole Dark Matter with Subaru HSC Microlensing Observations of M31</t>
+  </si>
+  <si>
+    <t>IPNS Joint Experimental-Theoretica Cosmology Seminar</t>
+  </si>
+  <si>
+    <t>Yuji Chinone</t>
   </si>
 </sst>
 </file>
@@ -3795,7 +3807,7 @@
       <c r="M38" s="8">
         <v>1</v>
       </c>
-      <c r="N38" s="16" t="s">
+      <c r="N38" s="38" t="s">
         <v>153</v>
       </c>
       <c r="O38" s="19" t="s">
@@ -4146,6 +4158,9 @@
       <c r="K48" s="57">
         <v>1</v>
       </c>
+      <c r="M48" s="40">
+        <v>1</v>
+      </c>
       <c r="N48" s="61" t="s">
         <v>207</v>
       </c>
@@ -4178,6 +4193,9 @@
       <c r="K49" s="47">
         <v>1</v>
       </c>
+      <c r="M49" s="1">
+        <v>1</v>
+      </c>
       <c r="N49" s="62" t="s">
         <v>214</v>
       </c>
@@ -4208,6 +4226,41 @@
         <v>1</v>
       </c>
       <c r="K50" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51" s="47">
+        <v>2026</v>
+      </c>
+      <c r="D51" s="47">
+        <v>6</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="47">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1</v>
+      </c>
+      <c r="N51" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="R51" s="33">
         <v>1</v>
       </c>
     </row>

--- a/talklists/talklist.xlsx
+++ b/talklists/talklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/writing/cv/talklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505ED053-D816-9142-853D-3EEEDDA05D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493EE602-5EF2-D94B-BA75-169598A7A210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="222">
   <si>
     <t>title</t>
   </si>
@@ -888,6 +888,12 @@
   </si>
   <si>
     <t>Yuji Chinone</t>
+  </si>
+  <si>
+    <t>https://astrophysics.uchicago.edu/events/event/2530/?past=y</t>
+  </si>
+  <si>
+    <t>https://roman-hlis-cosmology.caltech.edu/news/2024-f2f</t>
   </si>
 </sst>
 </file>
@@ -4065,6 +4071,9 @@
       <c r="N45" s="41" t="s">
         <v>199</v>
       </c>
+      <c r="O45" s="48" t="s">
+        <v>220</v>
+      </c>
       <c r="R45" s="47">
         <v>1</v>
       </c>
@@ -4090,6 +4099,9 @@
       </c>
       <c r="K46" s="57">
         <v>1</v>
+      </c>
+      <c r="O46" s="58" t="s">
+        <v>221</v>
       </c>
       <c r="R46" s="57">
         <v>1</v>
@@ -4301,6 +4313,8 @@
     <hyperlink ref="O47" r:id="rId32" location="20251205" xr:uid="{A78B1068-3E64-CE41-A412-3DC6F80D6967}"/>
     <hyperlink ref="O48" r:id="rId33" xr:uid="{14BD41FF-A6AC-E24B-BEE2-CD42174C8935}"/>
     <hyperlink ref="O49" r:id="rId34" xr:uid="{7FA0972F-0B7F-834A-A6FD-87E313E18CDA}"/>
+    <hyperlink ref="O45" r:id="rId35" xr:uid="{2352478C-31CE-D648-B159-05F52D2D7F99}"/>
+    <hyperlink ref="O46" r:id="rId36" xr:uid="{27B9BA78-A76E-4544-BD20-2EA63281B52A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/talklists/talklist.xlsx
+++ b/talklists/talklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sugiyamasunao/Documents/writing/cv/talklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493EE602-5EF2-D94B-BA75-169598A7A210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE69A62-EA3A-444E-977A-364E38C176C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="228">
   <si>
     <t>title</t>
   </si>
@@ -894,6 +894,24 @@
   </si>
   <si>
     <t>https://roman-hlis-cosmology.caltech.edu/news/2024-f2f</t>
+  </si>
+  <si>
+    <t>Observational exploration of primordial black holes</t>
+  </si>
+  <si>
+    <t>YITP</t>
+  </si>
+  <si>
+    <t>Progress in Partcles Physics</t>
+  </si>
+  <si>
+    <t>Kodai Sakurai</t>
+  </si>
+  <si>
+    <t>https://indico.yukawa.kyoto-u.ac.jp/event/95/overview</t>
+  </si>
+  <si>
+    <t>原始ブラックホールの観測的探査</t>
   </si>
 </sst>
 </file>
@@ -4276,7 +4294,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:18" s="40" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="40">
+        <v>2026</v>
+      </c>
+      <c r="D52" s="40">
+        <v>8</v>
+      </c>
+      <c r="E52" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="H52" s="40">
+        <v>1</v>
+      </c>
+      <c r="K52" s="40">
+        <v>1</v>
+      </c>
+      <c r="M52" s="40">
+        <v>1</v>
+      </c>
+      <c r="N52" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="O52" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q52" s="61"/>
+      <c r="R52" s="40">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4315,6 +4371,7 @@
     <hyperlink ref="O49" r:id="rId34" xr:uid="{7FA0972F-0B7F-834A-A6FD-87E313E18CDA}"/>
     <hyperlink ref="O45" r:id="rId35" xr:uid="{2352478C-31CE-D648-B159-05F52D2D7F99}"/>
     <hyperlink ref="O46" r:id="rId36" xr:uid="{27B9BA78-A76E-4544-BD20-2EA63281B52A}"/>
+    <hyperlink ref="O52" r:id="rId37" xr:uid="{4C59414C-6EB5-6641-B099-AE6C98E8A444}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
